--- a/outputs/32612.xlsx
+++ b/outputs/32612.xlsx
@@ -182,23 +182,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -414,13 +414,13 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -437,17 +437,17 @@
       <c r="D2" s="4" t="n">
         <v>0.172222222222222</v>
       </c>
-      <c r="E2" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A2)&gt;0,INDEX($J$2:$J$16,MATCH(A2,$I$2:$I$16,0)),TEXT(A2,"ddd"))</f>
+      <c r="E2" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A2,$I$2:$I$16,0))),VLOOKUP(A2,$I$2:$J$16,2,FALSE()),TEXT(A2,"ddd"))</f>
         <v>Mon</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>44927</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -464,17 +464,17 @@
       <c r="D3" s="4" t="n">
         <v>0.169444444444445</v>
       </c>
-      <c r="E3" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A3)&gt;0,INDEX($J$2:$J$16,MATCH(A3,$I$2:$I$16,0)),TEXT(A3,"ddd"))</f>
+      <c r="E3" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A3,$I$2:$I$16,0))),VLOOKUP(A3,$I$2:$J$16,2,FALSE()),TEXT(A3,"ddd"))</f>
         <v>Tue</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>44928</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -491,17 +491,17 @@
       <c r="D4" s="4" t="n">
         <v>0.172916666666667</v>
       </c>
-      <c r="E4" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A4)&gt;0,INDEX($J$2:$J$16,MATCH(A4,$I$2:$I$16,0)),TEXT(A4,"ddd"))</f>
+      <c r="E4" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A4,$I$2:$I$16,0))),VLOOKUP(A4,$I$2:$J$16,2,FALSE()),TEXT(A4,"ddd"))</f>
         <v>Wed</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>44952</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -518,17 +518,17 @@
       <c r="D5" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E5" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A5)&gt;0,INDEX($J$2:$J$16,MATCH(A5,$I$2:$I$16,0)),TEXT(A5,"ddd"))</f>
+      <c r="E5" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A5,$I$2:$I$16,0))),VLOOKUP(A5,$I$2:$J$16,2,FALSE()),TEXT(A5,"ddd"))</f>
         <v>Thu</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>44998</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -545,17 +545,17 @@
       <c r="D6" s="4" t="n">
         <v>0.167361111111111</v>
       </c>
-      <c r="E6" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A6)&gt;0,INDEX($J$2:$J$16,MATCH(A6,$I$2:$I$16,0)),TEXT(A6,"ddd"))</f>
+      <c r="E6" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A6,$I$2:$I$16,0))),VLOOKUP(A6,$I$2:$J$16,2,FALSE()),TEXT(A6,"ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>45023</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -572,17 +572,17 @@
       <c r="D7" s="4" t="n">
         <v>0.170833333333333</v>
       </c>
-      <c r="E7" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A7)&gt;0,INDEX($J$2:$J$16,MATCH(A7,$I$2:$I$16,0)),TEXT(A7,"ddd"))</f>
+      <c r="E7" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A7,$I$2:$I$16,0))),VLOOKUP(A7,$I$2:$J$16,2,FALSE()),TEXT(A7,"ddd"))</f>
         <v>Mon</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>45024</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -599,17 +599,17 @@
       <c r="D8" s="4" t="n">
         <v>0.169444444444445</v>
       </c>
-      <c r="E8" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A8)&gt;0,INDEX($J$2:$J$16,MATCH(A8,$I$2:$I$16,0)),TEXT(A8,"ddd"))</f>
+      <c r="E8" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A8,$I$2:$I$16,0))),VLOOKUP(A8,$I$2:$J$16,2,FALSE()),TEXT(A8,"ddd"))</f>
         <v>Tue</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>45025</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -626,17 +626,17 @@
       <c r="D9" s="4" t="n">
         <v>0.167361111111111</v>
       </c>
-      <c r="E9" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A9)&gt;0,INDEX($J$2:$J$16,MATCH(A9,$I$2:$I$16,0)),TEXT(A9,"ddd"))</f>
+      <c r="E9" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A9,$I$2:$I$16,0))),VLOOKUP(A9,$I$2:$J$16,2,FALSE()),TEXT(A9,"ddd"))</f>
         <v>Wed</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>45026</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -653,17 +653,17 @@
       <c r="D10" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E10" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A10)&gt;0,INDEX($J$2:$J$16,MATCH(A10,$I$2:$I$16,0)),TEXT(A10,"ddd"))</f>
+      <c r="E10" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A10,$I$2:$I$16,0))),VLOOKUP(A10,$I$2:$J$16,2,FALSE()),TEXT(A10,"ddd"))</f>
         <v>Thu</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>45393</v>
       </c>
-      <c r="J10" s="0" t="s">
+      <c r="J10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -680,17 +680,17 @@
       <c r="D11" s="4" t="n">
         <v>0.168055555555556</v>
       </c>
-      <c r="E11" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A11)&gt;0,INDEX($J$2:$J$16,MATCH(A11,$I$2:$I$16,0)),TEXT(A11,"ddd"))</f>
+      <c r="E11" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A11,$I$2:$I$16,0))),VLOOKUP(A11,$I$2:$J$16,2,FALSE()),TEXT(A11,"ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>45041</v>
       </c>
-      <c r="J11" s="0" t="s">
+      <c r="J11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -707,17 +707,17 @@
       <c r="D12" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E12" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A12)&gt;0,INDEX($J$2:$J$16,MATCH(A12,$I$2:$I$16,0)),TEXT(A12,"ddd"))</f>
+      <c r="E12" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A12,$I$2:$I$16,0))),VLOOKUP(A12,$I$2:$J$16,2,FALSE()),TEXT(A12,"ddd"))</f>
         <v>Mon</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>45089</v>
       </c>
-      <c r="J12" s="0" t="s">
+      <c r="J12" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -734,17 +734,17 @@
       <c r="D13" s="4" t="n">
         <v>0.169444444444445</v>
       </c>
-      <c r="E13" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A13)&gt;0,INDEX($J$2:$J$16,MATCH(A13,$I$2:$I$16,0)),TEXT(A13,"ddd"))</f>
+      <c r="E13" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A13,$I$2:$I$16,0))),VLOOKUP(A13,$I$2:$J$16,2,FALSE()),TEXT(A13,"ddd"))</f>
         <v>Wed</v>
       </c>
-      <c r="H13" s="0" t="s">
+      <c r="H13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>45198</v>
       </c>
-      <c r="J13" s="0" t="s">
+      <c r="J13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -761,17 +761,17 @@
       <c r="D14" s="4" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E14" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A14)&gt;0,INDEX($J$2:$J$16,MATCH(A14,$I$2:$I$16,0)),TEXT(A14,"ddd"))</f>
+      <c r="E14" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A14,$I$2:$I$16,0))),VLOOKUP(A14,$I$2:$J$16,2,FALSE()),TEXT(A14,"ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="H14" s="0" t="s">
+      <c r="H14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>45237</v>
       </c>
-      <c r="J14" s="0" t="s">
+      <c r="J14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -788,17 +788,17 @@
       <c r="D15" s="4" t="n">
         <v>0.16875</v>
       </c>
-      <c r="E15" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A15)&gt;0,INDEX($J$2:$J$16,MATCH(A15,$I$2:$I$16,0)),TEXT(A15,"ddd"))</f>
+      <c r="E15" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A15,$I$2:$I$16,0))),VLOOKUP(A15,$I$2:$J$16,2,FALSE()),TEXT(A15,"ddd"))</f>
         <v>Mon</v>
       </c>
-      <c r="H15" s="0" t="s">
+      <c r="H15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>45285</v>
       </c>
-      <c r="J15" s="0" t="s">
+      <c r="J15" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -815,17 +815,17 @@
       <c r="D16" s="4" t="n">
         <v>0.177083333333333</v>
       </c>
-      <c r="E16" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A16)&gt;0,INDEX($J$2:$J$16,MATCH(A16,$I$2:$I$16,0)),TEXT(A16,"ddd"))</f>
+      <c r="E16" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A16,$I$2:$I$16,0))),VLOOKUP(A16,$I$2:$J$16,2,FALSE()),TEXT(A16,"ddd"))</f>
         <v>Tue</v>
       </c>
-      <c r="H16" s="0" t="s">
+      <c r="H16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>45286</v>
       </c>
-      <c r="J16" s="0" t="s">
+      <c r="J16" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -842,8 +842,8 @@
       <c r="D17" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E17" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A17)&gt;0,INDEX($J$2:$J$16,MATCH(A17,$I$2:$I$16,0)),TEXT(A17,"ddd"))</f>
+      <c r="E17" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A17,$I$2:$I$16,0))),VLOOKUP(A17,$I$2:$J$16,2,FALSE()),TEXT(A17,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -860,8 +860,8 @@
       <c r="D18" s="4" t="n">
         <v>0.168055555555556</v>
       </c>
-      <c r="E18" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A18)&gt;0,INDEX($J$2:$J$16,MATCH(A18,$I$2:$I$16,0)),TEXT(A18,"ddd"))</f>
+      <c r="E18" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A18,$I$2:$I$16,0))),VLOOKUP(A18,$I$2:$J$16,2,FALSE()),TEXT(A18,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -878,8 +878,8 @@
       <c r="D19" s="4" t="n">
         <v>0.164583333333333</v>
       </c>
-      <c r="E19" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A19)&gt;0,INDEX($J$2:$J$16,MATCH(A19,$I$2:$I$16,0)),TEXT(A19,"ddd"))</f>
+      <c r="E19" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A19,$I$2:$I$16,0))),VLOOKUP(A19,$I$2:$J$16,2,FALSE()),TEXT(A19,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -896,8 +896,8 @@
       <c r="D20" s="4" t="n">
         <v>0.168055555555556</v>
       </c>
-      <c r="E20" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A20)&gt;0,INDEX($J$2:$J$16,MATCH(A20,$I$2:$I$16,0)),TEXT(A20,"ddd"))</f>
+      <c r="E20" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A20,$I$2:$I$16,0))),VLOOKUP(A20,$I$2:$J$16,2,FALSE()),TEXT(A20,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -914,8 +914,8 @@
       <c r="D21" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E21" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A21)&gt;0,INDEX($J$2:$J$16,MATCH(A21,$I$2:$I$16,0)),TEXT(A21,"ddd"))</f>
+      <c r="E21" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A21,$I$2:$I$16,0))),VLOOKUP(A21,$I$2:$J$16,2,FALSE()),TEXT(A21,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -932,8 +932,8 @@
       <c r="D22" s="4" t="n">
         <v>0.16875</v>
       </c>
-      <c r="E22" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A22)&gt;0,INDEX($J$2:$J$16,MATCH(A22,$I$2:$I$16,0)),TEXT(A22,"ddd"))</f>
+      <c r="E22" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A22,$I$2:$I$16,0))),VLOOKUP(A22,$I$2:$J$16,2,FALSE()),TEXT(A22,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -950,8 +950,8 @@
       <c r="D23" s="4" t="n">
         <v>0.165972222222222</v>
       </c>
-      <c r="E23" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A23)&gt;0,INDEX($J$2:$J$16,MATCH(A23,$I$2:$I$16,0)),TEXT(A23,"ddd"))</f>
+      <c r="E23" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A23,$I$2:$I$16,0))),VLOOKUP(A23,$I$2:$J$16,2,FALSE()),TEXT(A23,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -968,8 +968,8 @@
       <c r="D24" s="4" t="n">
         <v>0.175694444444444</v>
       </c>
-      <c r="E24" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A24)&gt;0,INDEX($J$2:$J$16,MATCH(A24,$I$2:$I$16,0)),TEXT(A24,"ddd"))</f>
+      <c r="E24" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A24,$I$2:$I$16,0))),VLOOKUP(A24,$I$2:$J$16,2,FALSE()),TEXT(A24,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -986,8 +986,8 @@
       <c r="D25" s="4" t="n">
         <v>0.168055555555556</v>
       </c>
-      <c r="E25" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A25)&gt;0,INDEX($J$2:$J$16,MATCH(A25,$I$2:$I$16,0)),TEXT(A25,"ddd"))</f>
+      <c r="E25" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A25,$I$2:$I$16,0))),VLOOKUP(A25,$I$2:$J$16,2,FALSE()),TEXT(A25,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1004,8 +1004,8 @@
       <c r="D26" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E26" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A26)&gt;0,INDEX($J$2:$J$16,MATCH(A26,$I$2:$I$16,0)),TEXT(A26,"ddd"))</f>
+      <c r="E26" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A26,$I$2:$I$16,0))),VLOOKUP(A26,$I$2:$J$16,2,FALSE()),TEXT(A26,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1022,8 +1022,8 @@
       <c r="D27" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E27" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A27)&gt;0,INDEX($J$2:$J$16,MATCH(A27,$I$2:$I$16,0)),TEXT(A27,"ddd"))</f>
+      <c r="E27" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A27,$I$2:$I$16,0))),VLOOKUP(A27,$I$2:$J$16,2,FALSE()),TEXT(A27,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1040,8 +1040,8 @@
       <c r="D28" s="4" t="n">
         <v>0.159722222222222</v>
       </c>
-      <c r="E28" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A28)&gt;0,INDEX($J$2:$J$16,MATCH(A28,$I$2:$I$16,0)),TEXT(A28,"ddd"))</f>
+      <c r="E28" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A28,$I$2:$I$16,0))),VLOOKUP(A28,$I$2:$J$16,2,FALSE()),TEXT(A28,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1058,8 +1058,8 @@
       <c r="D29" s="4" t="n">
         <v>0.170833333333333</v>
       </c>
-      <c r="E29" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A29)&gt;0,INDEX($J$2:$J$16,MATCH(A29,$I$2:$I$16,0)),TEXT(A29,"ddd"))</f>
+      <c r="E29" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A29,$I$2:$I$16,0))),VLOOKUP(A29,$I$2:$J$16,2,FALSE()),TEXT(A29,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1076,8 +1076,8 @@
       <c r="D30" s="4" t="n">
         <v>0.163194444444444</v>
       </c>
-      <c r="E30" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A30)&gt;0,INDEX($J$2:$J$16,MATCH(A30,$I$2:$I$16,0)),TEXT(A30,"ddd"))</f>
+      <c r="E30" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A30,$I$2:$I$16,0))),VLOOKUP(A30,$I$2:$J$16,2,FALSE()),TEXT(A30,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1094,8 +1094,8 @@
       <c r="D31" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E31" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A31)&gt;0,INDEX($J$2:$J$16,MATCH(A31,$I$2:$I$16,0)),TEXT(A31,"ddd"))</f>
+      <c r="E31" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A31,$I$2:$I$16,0))),VLOOKUP(A31,$I$2:$J$16,2,FALSE()),TEXT(A31,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1112,8 +1112,8 @@
       <c r="D32" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E32" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A32)&gt;0,INDEX($J$2:$J$16,MATCH(A32,$I$2:$I$16,0)),TEXT(A32,"ddd"))</f>
+      <c r="E32" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A32,$I$2:$I$16,0))),VLOOKUP(A32,$I$2:$J$16,2,FALSE()),TEXT(A32,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1130,8 +1130,8 @@
       <c r="D33" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E33" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A33)&gt;0,INDEX($J$2:$J$16,MATCH(A33,$I$2:$I$16,0)),TEXT(A33,"ddd"))</f>
+      <c r="E33" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A33,$I$2:$I$16,0))),VLOOKUP(A33,$I$2:$J$16,2,FALSE()),TEXT(A33,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1148,8 +1148,8 @@
       <c r="D34" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E34" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A34)&gt;0,INDEX($J$2:$J$16,MATCH(A34,$I$2:$I$16,0)),TEXT(A34,"ddd"))</f>
+      <c r="E34" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A34,$I$2:$I$16,0))),VLOOKUP(A34,$I$2:$J$16,2,FALSE()),TEXT(A34,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1166,8 +1166,8 @@
       <c r="D35" s="4" t="n">
         <v>0.167361111111111</v>
       </c>
-      <c r="E35" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A35)&gt;0,INDEX($J$2:$J$16,MATCH(A35,$I$2:$I$16,0)),TEXT(A35,"ddd"))</f>
+      <c r="E35" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A35,$I$2:$I$16,0))),VLOOKUP(A35,$I$2:$J$16,2,FALSE()),TEXT(A35,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1184,8 +1184,8 @@
       <c r="D36" s="4" t="n">
         <v>0.172222222222222</v>
       </c>
-      <c r="E36" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A36)&gt;0,INDEX($J$2:$J$16,MATCH(A36,$I$2:$I$16,0)),TEXT(A36,"ddd"))</f>
+      <c r="E36" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A36,$I$2:$I$16,0))),VLOOKUP(A36,$I$2:$J$16,2,FALSE()),TEXT(A36,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1202,8 +1202,8 @@
       <c r="D37" s="4" t="n">
         <v>0.181944444444444</v>
       </c>
-      <c r="E37" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A37)&gt;0,INDEX($J$2:$J$16,MATCH(A37,$I$2:$I$16,0)),TEXT(A37,"ddd"))</f>
+      <c r="E37" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A37,$I$2:$I$16,0))),VLOOKUP(A37,$I$2:$J$16,2,FALSE()),TEXT(A37,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1220,8 +1220,8 @@
       <c r="D38" s="4" t="n">
         <v>0.165277777777778</v>
       </c>
-      <c r="E38" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A38)&gt;0,INDEX($J$2:$J$16,MATCH(A38,$I$2:$I$16,0)),TEXT(A38,"ddd"))</f>
+      <c r="E38" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A38,$I$2:$I$16,0))),VLOOKUP(A38,$I$2:$J$16,2,FALSE()),TEXT(A38,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1238,8 +1238,8 @@
       <c r="D39" s="4" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E39" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A39)&gt;0,INDEX($J$2:$J$16,MATCH(A39,$I$2:$I$16,0)),TEXT(A39,"ddd"))</f>
+      <c r="E39" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A39,$I$2:$I$16,0))),VLOOKUP(A39,$I$2:$J$16,2,FALSE()),TEXT(A39,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1256,8 +1256,8 @@
       <c r="D40" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E40" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A40)&gt;0,INDEX($J$2:$J$16,MATCH(A40,$I$2:$I$16,0)),TEXT(A40,"ddd"))</f>
+      <c r="E40" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A40,$I$2:$I$16,0))),VLOOKUP(A40,$I$2:$J$16,2,FALSE()),TEXT(A40,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1274,8 +1274,8 @@
       <c r="D41" s="4" t="n">
         <v>0.169444444444445</v>
       </c>
-      <c r="E41" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A41)&gt;0,INDEX($J$2:$J$16,MATCH(A41,$I$2:$I$16,0)),TEXT(A41,"ddd"))</f>
+      <c r="E41" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A41,$I$2:$I$16,0))),VLOOKUP(A41,$I$2:$J$16,2,FALSE()),TEXT(A41,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1292,8 +1292,8 @@
       <c r="D42" s="4" t="n">
         <v>0.163888888888889</v>
       </c>
-      <c r="E42" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A42)&gt;0,INDEX($J$2:$J$16,MATCH(A42,$I$2:$I$16,0)),TEXT(A42,"ddd"))</f>
+      <c r="E42" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A42,$I$2:$I$16,0))),VLOOKUP(A42,$I$2:$J$16,2,FALSE()),TEXT(A42,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1310,8 +1310,8 @@
       <c r="D43" s="4" t="n">
         <v>0.165277777777778</v>
       </c>
-      <c r="E43" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A43)&gt;0,INDEX($J$2:$J$16,MATCH(A43,$I$2:$I$16,0)),TEXT(A43,"ddd"))</f>
+      <c r="E43" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A43,$I$2:$I$16,0))),VLOOKUP(A43,$I$2:$J$16,2,FALSE()),TEXT(A43,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1328,8 +1328,8 @@
       <c r="D44" s="4" t="n">
         <v>0.170833333333333</v>
       </c>
-      <c r="E44" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A44)&gt;0,INDEX($J$2:$J$16,MATCH(A44,$I$2:$I$16,0)),TEXT(A44,"ddd"))</f>
+      <c r="E44" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A44,$I$2:$I$16,0))),VLOOKUP(A44,$I$2:$J$16,2,FALSE()),TEXT(A44,"ddd"))</f>
         <v>PH(working)</v>
       </c>
     </row>
@@ -1346,8 +1346,8 @@
       <c r="D45" s="4" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E45" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A45)&gt;0,INDEX($J$2:$J$16,MATCH(A45,$I$2:$I$16,0)),TEXT(A45,"ddd"))</f>
+      <c r="E45" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A45,$I$2:$I$16,0))),VLOOKUP(A45,$I$2:$J$16,2,FALSE()),TEXT(A45,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1364,8 +1364,8 @@
       <c r="D46" s="4" t="n">
         <v>0.170138888888889</v>
       </c>
-      <c r="E46" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A46)&gt;0,INDEX($J$2:$J$16,MATCH(A46,$I$2:$I$16,0)),TEXT(A46,"ddd"))</f>
+      <c r="E46" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A46,$I$2:$I$16,0))),VLOOKUP(A46,$I$2:$J$16,2,FALSE()),TEXT(A46,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1382,8 +1382,8 @@
       <c r="D47" s="4" t="n">
         <v>0.18125</v>
       </c>
-      <c r="E47" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A47)&gt;0,INDEX($J$2:$J$16,MATCH(A47,$I$2:$I$16,0)),TEXT(A47,"ddd"))</f>
+      <c r="E47" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A47,$I$2:$I$16,0))),VLOOKUP(A47,$I$2:$J$16,2,FALSE()),TEXT(A47,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1400,8 +1400,8 @@
       <c r="D48" s="4" t="n">
         <v>0.173611111111111</v>
       </c>
-      <c r="E48" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A48)&gt;0,INDEX($J$2:$J$16,MATCH(A48,$I$2:$I$16,0)),TEXT(A48,"ddd"))</f>
+      <c r="E48" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A48,$I$2:$I$16,0))),VLOOKUP(A48,$I$2:$J$16,2,FALSE()),TEXT(A48,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1418,8 +1418,8 @@
       <c r="D49" s="4" t="n">
         <v>0.172222222222222</v>
       </c>
-      <c r="E49" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A49)&gt;0,INDEX($J$2:$J$16,MATCH(A49,$I$2:$I$16,0)),TEXT(A49,"ddd"))</f>
+      <c r="E49" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A49,$I$2:$I$16,0))),VLOOKUP(A49,$I$2:$J$16,2,FALSE()),TEXT(A49,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1436,8 +1436,8 @@
       <c r="D50" s="4" t="n">
         <v>0.167361111111111</v>
       </c>
-      <c r="E50" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A50)&gt;0,INDEX($J$2:$J$16,MATCH(A50,$I$2:$I$16,0)),TEXT(A50,"ddd"))</f>
+      <c r="E50" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A50,$I$2:$I$16,0))),VLOOKUP(A50,$I$2:$J$16,2,FALSE()),TEXT(A50,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1454,8 +1454,8 @@
       <c r="D51" s="4" t="n">
         <v>0.167361111111111</v>
       </c>
-      <c r="E51" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A51)&gt;0,INDEX($J$2:$J$16,MATCH(A51,$I$2:$I$16,0)),TEXT(A51,"ddd"))</f>
+      <c r="E51" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A51,$I$2:$I$16,0))),VLOOKUP(A51,$I$2:$J$16,2,FALSE()),TEXT(A51,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1472,8 +1472,8 @@
       <c r="D52" s="4" t="n">
         <v>0.172222222222222</v>
       </c>
-      <c r="E52" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A52)&gt;0,INDEX($J$2:$J$16,MATCH(A52,$I$2:$I$16,0)),TEXT(A52,"ddd"))</f>
+      <c r="E52" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A52,$I$2:$I$16,0))),VLOOKUP(A52,$I$2:$J$16,2,FALSE()),TEXT(A52,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1490,8 +1490,8 @@
       <c r="D53" s="4" t="n">
         <v>0.173611111111111</v>
       </c>
-      <c r="E53" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A53)&gt;0,INDEX($J$2:$J$16,MATCH(A53,$I$2:$I$16,0)),TEXT(A53,"ddd"))</f>
+      <c r="E53" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A53,$I$2:$I$16,0))),VLOOKUP(A53,$I$2:$J$16,2,FALSE()),TEXT(A53,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1508,8 +1508,8 @@
       <c r="D54" s="4" t="n">
         <v>0.176388888888889</v>
       </c>
-      <c r="E54" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A54)&gt;0,INDEX($J$2:$J$16,MATCH(A54,$I$2:$I$16,0)),TEXT(A54,"ddd"))</f>
+      <c r="E54" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A54,$I$2:$I$16,0))),VLOOKUP(A54,$I$2:$J$16,2,FALSE()),TEXT(A54,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1526,8 +1526,8 @@
       <c r="D55" s="4" t="n">
         <v>0.174305555555556</v>
       </c>
-      <c r="E55" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A55)&gt;0,INDEX($J$2:$J$16,MATCH(A55,$I$2:$I$16,0)),TEXT(A55,"ddd"))</f>
+      <c r="E55" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A55,$I$2:$I$16,0))),VLOOKUP(A55,$I$2:$J$16,2,FALSE()),TEXT(A55,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1544,8 +1544,8 @@
       <c r="D56" s="4" t="n">
         <v>0.170833333333333</v>
       </c>
-      <c r="E56" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A56)&gt;0,INDEX($J$2:$J$16,MATCH(A56,$I$2:$I$16,0)),TEXT(A56,"ddd"))</f>
+      <c r="E56" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A56,$I$2:$I$16,0))),VLOOKUP(A56,$I$2:$J$16,2,FALSE()),TEXT(A56,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1562,8 +1562,8 @@
       <c r="D57" s="4" t="n">
         <v>0.165277777777778</v>
       </c>
-      <c r="E57" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A57)&gt;0,INDEX($J$2:$J$16,MATCH(A57,$I$2:$I$16,0)),TEXT(A57,"ddd"))</f>
+      <c r="E57" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A57,$I$2:$I$16,0))),VLOOKUP(A57,$I$2:$J$16,2,FALSE()),TEXT(A57,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1580,8 +1580,8 @@
       <c r="D58" s="4" t="n">
         <v>0.175694444444444</v>
       </c>
-      <c r="E58" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A58)&gt;0,INDEX($J$2:$J$16,MATCH(A58,$I$2:$I$16,0)),TEXT(A58,"ddd"))</f>
+      <c r="E58" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A58,$I$2:$I$16,0))),VLOOKUP(A58,$I$2:$J$16,2,FALSE()),TEXT(A58,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1598,8 +1598,8 @@
       <c r="D59" s="4" t="n">
         <v>0.168055555555556</v>
       </c>
-      <c r="E59" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A59)&gt;0,INDEX($J$2:$J$16,MATCH(A59,$I$2:$I$16,0)),TEXT(A59,"ddd"))</f>
+      <c r="E59" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A59,$I$2:$I$16,0))),VLOOKUP(A59,$I$2:$J$16,2,FALSE()),TEXT(A59,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1616,8 +1616,8 @@
       <c r="D60" s="4" t="n">
         <v>0.165277777777778</v>
       </c>
-      <c r="E60" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A60)&gt;0,INDEX($J$2:$J$16,MATCH(A60,$I$2:$I$16,0)),TEXT(A60,"ddd"))</f>
+      <c r="E60" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A60,$I$2:$I$16,0))),VLOOKUP(A60,$I$2:$J$16,2,FALSE()),TEXT(A60,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1634,8 +1634,8 @@
       <c r="D61" s="4" t="n">
         <v>0.16875</v>
       </c>
-      <c r="E61" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A61)&gt;0,INDEX($J$2:$J$16,MATCH(A61,$I$2:$I$16,0)),TEXT(A61,"ddd"))</f>
+      <c r="E61" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A61,$I$2:$I$16,0))),VLOOKUP(A61,$I$2:$J$16,2,FALSE()),TEXT(A61,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1652,8 +1652,8 @@
       <c r="D62" s="4" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E62" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A62)&gt;0,INDEX($J$2:$J$16,MATCH(A62,$I$2:$I$16,0)),TEXT(A62,"ddd"))</f>
+      <c r="E62" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A62,$I$2:$I$16,0))),VLOOKUP(A62,$I$2:$J$16,2,FALSE()),TEXT(A62,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1670,8 +1670,8 @@
       <c r="D63" s="4" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E63" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A63)&gt;0,INDEX($J$2:$J$16,MATCH(A63,$I$2:$I$16,0)),TEXT(A63,"ddd"))</f>
+      <c r="E63" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A63,$I$2:$I$16,0))),VLOOKUP(A63,$I$2:$J$16,2,FALSE()),TEXT(A63,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1688,8 +1688,8 @@
       <c r="D64" s="4" t="n">
         <v>0.172916666666667</v>
       </c>
-      <c r="E64" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A64)&gt;0,INDEX($J$2:$J$16,MATCH(A64,$I$2:$I$16,0)),TEXT(A64,"ddd"))</f>
+      <c r="E64" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A64,$I$2:$I$16,0))),VLOOKUP(A64,$I$2:$J$16,2,FALSE()),TEXT(A64,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1706,8 +1706,8 @@
       <c r="D65" s="4" t="n">
         <v>0.170833333333333</v>
       </c>
-      <c r="E65" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A65)&gt;0,INDEX($J$2:$J$16,MATCH(A65,$I$2:$I$16,0)),TEXT(A65,"ddd"))</f>
+      <c r="E65" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A65,$I$2:$I$16,0))),VLOOKUP(A65,$I$2:$J$16,2,FALSE()),TEXT(A65,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1724,8 +1724,8 @@
       <c r="D66" s="4" t="n">
         <v>0.173611111111111</v>
       </c>
-      <c r="E66" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A66)&gt;0,INDEX($J$2:$J$16,MATCH(A66,$I$2:$I$16,0)),TEXT(A66,"ddd"))</f>
+      <c r="E66" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A66,$I$2:$I$16,0))),VLOOKUP(A66,$I$2:$J$16,2,FALSE()),TEXT(A66,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1742,8 +1742,8 @@
       <c r="D67" s="4" t="n">
         <v>0.173611111111111</v>
       </c>
-      <c r="E67" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A67)&gt;0,INDEX($J$2:$J$16,MATCH(A67,$I$2:$I$16,0)),TEXT(A67,"ddd"))</f>
+      <c r="E67" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A67,$I$2:$I$16,0))),VLOOKUP(A67,$I$2:$J$16,2,FALSE()),TEXT(A67,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1760,8 +1760,8 @@
       <c r="D68" s="4" t="n">
         <v>0.177083333333333</v>
       </c>
-      <c r="E68" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A68)&gt;0,INDEX($J$2:$J$16,MATCH(A68,$I$2:$I$16,0)),TEXT(A68,"ddd"))</f>
+      <c r="E68" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A68,$I$2:$I$16,0))),VLOOKUP(A68,$I$2:$J$16,2,FALSE()),TEXT(A68,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1778,8 +1778,8 @@
       <c r="D69" s="4" t="n">
         <v>0.181944444444444</v>
       </c>
-      <c r="E69" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A69)&gt;0,INDEX($J$2:$J$16,MATCH(A69,$I$2:$I$16,0)),TEXT(A69,"ddd"))</f>
+      <c r="E69" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A69,$I$2:$I$16,0))),VLOOKUP(A69,$I$2:$J$16,2,FALSE()),TEXT(A69,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1796,8 +1796,8 @@
       <c r="D70" s="4" t="n">
         <v>0.171527777777778</v>
       </c>
-      <c r="E70" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A70)&gt;0,INDEX($J$2:$J$16,MATCH(A70,$I$2:$I$16,0)),TEXT(A70,"ddd"))</f>
+      <c r="E70" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A70,$I$2:$I$16,0))),VLOOKUP(A70,$I$2:$J$16,2,FALSE()),TEXT(A70,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1814,8 +1814,8 @@
       <c r="D71" s="4" t="n">
         <v>0.172222222222222</v>
       </c>
-      <c r="E71" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A71)&gt;0,INDEX($J$2:$J$16,MATCH(A71,$I$2:$I$16,0)),TEXT(A71,"ddd"))</f>
+      <c r="E71" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A71,$I$2:$I$16,0))),VLOOKUP(A71,$I$2:$J$16,2,FALSE()),TEXT(A71,"ddd"))</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1832,8 +1832,8 @@
       <c r="D72" s="4" t="n">
         <v>0.175</v>
       </c>
-      <c r="E72" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A72)&gt;0,INDEX($J$2:$J$16,MATCH(A72,$I$2:$I$16,0)),TEXT(A72,"ddd"))</f>
+      <c r="E72" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A72,$I$2:$I$16,0))),VLOOKUP(A72,$I$2:$J$16,2,FALSE()),TEXT(A72,"ddd"))</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1850,8 +1850,8 @@
       <c r="D73" s="4" t="n">
         <v>0.175</v>
       </c>
-      <c r="E73" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A73)&gt;0,INDEX($J$2:$J$16,MATCH(A73,$I$2:$I$16,0)),TEXT(A73,"ddd"))</f>
+      <c r="E73" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A73,$I$2:$I$16,0))),VLOOKUP(A73,$I$2:$J$16,2,FALSE()),TEXT(A73,"ddd"))</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1868,8 +1868,8 @@
       <c r="D74" s="4" t="n">
         <v>0.172222222222222</v>
       </c>
-      <c r="E74" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A74)&gt;0,INDEX($J$2:$J$16,MATCH(A74,$I$2:$I$16,0)),TEXT(A74,"ddd"))</f>
+      <c r="E74" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A74,$I$2:$I$16,0))),VLOOKUP(A74,$I$2:$J$16,2,FALSE()),TEXT(A74,"ddd"))</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1886,8 +1886,8 @@
       <c r="D75" s="4" t="n">
         <v>0.165972222222222</v>
       </c>
-      <c r="E75" s="0" t="str">
-        <f aca="false">IF(COUNTIF($I$2:$I$16,A75)&gt;0,INDEX($J$2:$J$16,MATCH(A75,$I$2:$I$16,0)),TEXT(A75,"ddd"))</f>
+      <c r="E75" s="1" t="str">
+        <f aca="false">IF(NOT(ISNA(MATCH(A75,$I$2:$I$16,0))),VLOOKUP(A75,$I$2:$J$16,2,FALSE()),TEXT(A75,"ddd"))</f>
         <v>Fri</v>
       </c>
     </row>

--- a/outputs/32612.xlsx
+++ b/outputs/32612.xlsx
@@ -438,7 +438,7 @@
         <v>0.172222222222222</v>
       </c>
       <c r="E2" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A2,$I$2:$I$16,0))),VLOOKUP(A2,$I$2:$J$16,2,FALSE()),TEXT(A2,"ddd"))</f>
+        <f aca="false">TEXT(A2,"ddd")</f>
         <v>Mon</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -465,7 +465,7 @@
         <v>0.169444444444445</v>
       </c>
       <c r="E3" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A3,$I$2:$I$16,0))),VLOOKUP(A3,$I$2:$J$16,2,FALSE()),TEXT(A3,"ddd"))</f>
+        <f aca="false">TEXT(A3,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -492,7 +492,7 @@
         <v>0.172916666666667</v>
       </c>
       <c r="E4" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A4,$I$2:$I$16,0))),VLOOKUP(A4,$I$2:$J$16,2,FALSE()),TEXT(A4,"ddd"))</f>
+        <f aca="false">TEXT(A4,"ddd")</f>
         <v>Wed</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -519,7 +519,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E5" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A5,$I$2:$I$16,0))),VLOOKUP(A5,$I$2:$J$16,2,FALSE()),TEXT(A5,"ddd"))</f>
+        <f aca="false">TEXT(A5,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -546,7 +546,7 @@
         <v>0.167361111111111</v>
       </c>
       <c r="E6" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A6,$I$2:$I$16,0))),VLOOKUP(A6,$I$2:$J$16,2,FALSE()),TEXT(A6,"ddd"))</f>
+        <f aca="false">TEXT(A6,"ddd")</f>
         <v>Fri</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -573,7 +573,7 @@
         <v>0.170833333333333</v>
       </c>
       <c r="E7" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A7,$I$2:$I$16,0))),VLOOKUP(A7,$I$2:$J$16,2,FALSE()),TEXT(A7,"ddd"))</f>
+        <f aca="false">TEXT(A7,"ddd")</f>
         <v>Mon</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -600,7 +600,7 @@
         <v>0.169444444444445</v>
       </c>
       <c r="E8" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A8,$I$2:$I$16,0))),VLOOKUP(A8,$I$2:$J$16,2,FALSE()),TEXT(A8,"ddd"))</f>
+        <f aca="false">TEXT(A8,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -627,7 +627,7 @@
         <v>0.167361111111111</v>
       </c>
       <c r="E9" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A9,$I$2:$I$16,0))),VLOOKUP(A9,$I$2:$J$16,2,FALSE()),TEXT(A9,"ddd"))</f>
+        <f aca="false">TEXT(A9,"ddd")</f>
         <v>Wed</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -654,7 +654,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E10" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A10,$I$2:$I$16,0))),VLOOKUP(A10,$I$2:$J$16,2,FALSE()),TEXT(A10,"ddd"))</f>
+        <f aca="false">TEXT(A10,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -681,7 +681,7 @@
         <v>0.168055555555556</v>
       </c>
       <c r="E11" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A11,$I$2:$I$16,0))),VLOOKUP(A11,$I$2:$J$16,2,FALSE()),TEXT(A11,"ddd"))</f>
+        <f aca="false">TEXT(A11,"ddd")</f>
         <v>Fri</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -708,7 +708,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E12" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A12,$I$2:$I$16,0))),VLOOKUP(A12,$I$2:$J$16,2,FALSE()),TEXT(A12,"ddd"))</f>
+        <f aca="false">TEXT(A12,"ddd")</f>
         <v>Mon</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -735,7 +735,7 @@
         <v>0.169444444444445</v>
       </c>
       <c r="E13" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A13,$I$2:$I$16,0))),VLOOKUP(A13,$I$2:$J$16,2,FALSE()),TEXT(A13,"ddd"))</f>
+        <f aca="false">TEXT(A13,"ddd")</f>
         <v>Wed</v>
       </c>
       <c r="H13" s="1" t="s">
@@ -762,7 +762,7 @@
         <v>0.166666666666667</v>
       </c>
       <c r="E14" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A14,$I$2:$I$16,0))),VLOOKUP(A14,$I$2:$J$16,2,FALSE()),TEXT(A14,"ddd"))</f>
+        <f aca="false">TEXT(A14,"ddd")</f>
         <v>Fri</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -789,7 +789,7 @@
         <v>0.16875</v>
       </c>
       <c r="E15" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A15,$I$2:$I$16,0))),VLOOKUP(A15,$I$2:$J$16,2,FALSE()),TEXT(A15,"ddd"))</f>
+        <f aca="false">TEXT(A15,"ddd")</f>
         <v>Mon</v>
       </c>
       <c r="H15" s="1" t="s">
@@ -816,7 +816,7 @@
         <v>0.177083333333333</v>
       </c>
       <c r="E16" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A16,$I$2:$I$16,0))),VLOOKUP(A16,$I$2:$J$16,2,FALSE()),TEXT(A16,"ddd"))</f>
+        <f aca="false">TEXT(A16,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="H16" s="1" t="s">
@@ -843,7 +843,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E17" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A17,$I$2:$I$16,0))),VLOOKUP(A17,$I$2:$J$16,2,FALSE()),TEXT(A17,"ddd"))</f>
+        <f aca="false">TEXT(A17,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -861,7 +861,7 @@
         <v>0.168055555555556</v>
       </c>
       <c r="E18" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A18,$I$2:$I$16,0))),VLOOKUP(A18,$I$2:$J$16,2,FALSE()),TEXT(A18,"ddd"))</f>
+        <f aca="false">TEXT(A18,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>0.164583333333333</v>
       </c>
       <c r="E19" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A19,$I$2:$I$16,0))),VLOOKUP(A19,$I$2:$J$16,2,FALSE()),TEXT(A19,"ddd"))</f>
+        <f aca="false">TEXT(A19,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -897,7 +897,7 @@
         <v>0.168055555555556</v>
       </c>
       <c r="E20" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A20,$I$2:$I$16,0))),VLOOKUP(A20,$I$2:$J$16,2,FALSE()),TEXT(A20,"ddd"))</f>
+        <f aca="false">TEXT(A20,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -915,7 +915,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E21" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A21,$I$2:$I$16,0))),VLOOKUP(A21,$I$2:$J$16,2,FALSE()),TEXT(A21,"ddd"))</f>
+        <f aca="false">TEXT(A21,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -933,7 +933,7 @@
         <v>0.16875</v>
       </c>
       <c r="E22" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A22,$I$2:$I$16,0))),VLOOKUP(A22,$I$2:$J$16,2,FALSE()),TEXT(A22,"ddd"))</f>
+        <f aca="false">TEXT(A22,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>0.165972222222222</v>
       </c>
       <c r="E23" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A23,$I$2:$I$16,0))),VLOOKUP(A23,$I$2:$J$16,2,FALSE()),TEXT(A23,"ddd"))</f>
+        <f aca="false">TEXT(A23,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>0.175694444444444</v>
       </c>
       <c r="E24" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A24,$I$2:$I$16,0))),VLOOKUP(A24,$I$2:$J$16,2,FALSE()),TEXT(A24,"ddd"))</f>
+        <f aca="false">TEXT(A24,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -987,7 +987,7 @@
         <v>0.168055555555556</v>
       </c>
       <c r="E25" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A25,$I$2:$I$16,0))),VLOOKUP(A25,$I$2:$J$16,2,FALSE()),TEXT(A25,"ddd"))</f>
+        <f aca="false">TEXT(A25,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E26" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A26,$I$2:$I$16,0))),VLOOKUP(A26,$I$2:$J$16,2,FALSE()),TEXT(A26,"ddd"))</f>
+        <f aca="false">TEXT(A26,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E27" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A27,$I$2:$I$16,0))),VLOOKUP(A27,$I$2:$J$16,2,FALSE()),TEXT(A27,"ddd"))</f>
+        <f aca="false">TEXT(A27,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         <v>0.159722222222222</v>
       </c>
       <c r="E28" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A28,$I$2:$I$16,0))),VLOOKUP(A28,$I$2:$J$16,2,FALSE()),TEXT(A28,"ddd"))</f>
+        <f aca="false">TEXT(A28,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
         <v>0.170833333333333</v>
       </c>
       <c r="E29" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A29,$I$2:$I$16,0))),VLOOKUP(A29,$I$2:$J$16,2,FALSE()),TEXT(A29,"ddd"))</f>
+        <f aca="false">TEXT(A29,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         <v>0.163194444444444</v>
       </c>
       <c r="E30" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A30,$I$2:$I$16,0))),VLOOKUP(A30,$I$2:$J$16,2,FALSE()),TEXT(A30,"ddd"))</f>
+        <f aca="false">TEXT(A30,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E31" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A31,$I$2:$I$16,0))),VLOOKUP(A31,$I$2:$J$16,2,FALSE()),TEXT(A31,"ddd"))</f>
+        <f aca="false">TEXT(A31,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E32" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A32,$I$2:$I$16,0))),VLOOKUP(A32,$I$2:$J$16,2,FALSE()),TEXT(A32,"ddd"))</f>
+        <f aca="false">TEXT(A32,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E33" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A33,$I$2:$I$16,0))),VLOOKUP(A33,$I$2:$J$16,2,FALSE()),TEXT(A33,"ddd"))</f>
+        <f aca="false">TEXT(A33,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E34" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A34,$I$2:$I$16,0))),VLOOKUP(A34,$I$2:$J$16,2,FALSE()),TEXT(A34,"ddd"))</f>
+        <f aca="false">TEXT(A34,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>0.167361111111111</v>
       </c>
       <c r="E35" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A35,$I$2:$I$16,0))),VLOOKUP(A35,$I$2:$J$16,2,FALSE()),TEXT(A35,"ddd"))</f>
+        <f aca="false">TEXT(A35,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
         <v>0.172222222222222</v>
       </c>
       <c r="E36" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A36,$I$2:$I$16,0))),VLOOKUP(A36,$I$2:$J$16,2,FALSE()),TEXT(A36,"ddd"))</f>
+        <f aca="false">TEXT(A36,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
         <v>0.181944444444444</v>
       </c>
       <c r="E37" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A37,$I$2:$I$16,0))),VLOOKUP(A37,$I$2:$J$16,2,FALSE()),TEXT(A37,"ddd"))</f>
+        <f aca="false">TEXT(A37,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
         <v>0.165277777777778</v>
       </c>
       <c r="E38" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A38,$I$2:$I$16,0))),VLOOKUP(A38,$I$2:$J$16,2,FALSE()),TEXT(A38,"ddd"))</f>
+        <f aca="false">TEXT(A38,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>0.166666666666667</v>
       </c>
       <c r="E39" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A39,$I$2:$I$16,0))),VLOOKUP(A39,$I$2:$J$16,2,FALSE()),TEXT(A39,"ddd"))</f>
+        <f aca="false">TEXT(A39,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E40" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A40,$I$2:$I$16,0))),VLOOKUP(A40,$I$2:$J$16,2,FALSE()),TEXT(A40,"ddd"))</f>
+        <f aca="false">TEXT(A40,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         <v>0.169444444444445</v>
       </c>
       <c r="E41" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A41,$I$2:$I$16,0))),VLOOKUP(A41,$I$2:$J$16,2,FALSE()),TEXT(A41,"ddd"))</f>
+        <f aca="false">TEXT(A41,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
         <v>0.163888888888889</v>
       </c>
       <c r="E42" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A42,$I$2:$I$16,0))),VLOOKUP(A42,$I$2:$J$16,2,FALSE()),TEXT(A42,"ddd"))</f>
+        <f aca="false">TEXT(A42,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
         <v>0.165277777777778</v>
       </c>
       <c r="E43" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A43,$I$2:$I$16,0))),VLOOKUP(A43,$I$2:$J$16,2,FALSE()),TEXT(A43,"ddd"))</f>
+        <f aca="false">TEXT(A43,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1329,8 +1329,8 @@
         <v>0.170833333333333</v>
       </c>
       <c r="E44" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A44,$I$2:$I$16,0))),VLOOKUP(A44,$I$2:$J$16,2,FALSE()),TEXT(A44,"ddd"))</f>
-        <v>PH(working)</v>
+        <f aca="false">TEXT(A44,"ddd")</f>
+        <v>Mon</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1347,7 +1347,7 @@
         <v>0.166666666666667</v>
       </c>
       <c r="E45" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A45,$I$2:$I$16,0))),VLOOKUP(A45,$I$2:$J$16,2,FALSE()),TEXT(A45,"ddd"))</f>
+        <f aca="false">TEXT(A45,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         <v>0.170138888888889</v>
       </c>
       <c r="E46" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A46,$I$2:$I$16,0))),VLOOKUP(A46,$I$2:$J$16,2,FALSE()),TEXT(A46,"ddd"))</f>
+        <f aca="false">TEXT(A46,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>0.18125</v>
       </c>
       <c r="E47" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A47,$I$2:$I$16,0))),VLOOKUP(A47,$I$2:$J$16,2,FALSE()),TEXT(A47,"ddd"))</f>
+        <f aca="false">TEXT(A47,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>0.173611111111111</v>
       </c>
       <c r="E48" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A48,$I$2:$I$16,0))),VLOOKUP(A48,$I$2:$J$16,2,FALSE()),TEXT(A48,"ddd"))</f>
+        <f aca="false">TEXT(A48,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
         <v>0.172222222222222</v>
       </c>
       <c r="E49" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A49,$I$2:$I$16,0))),VLOOKUP(A49,$I$2:$J$16,2,FALSE()),TEXT(A49,"ddd"))</f>
+        <f aca="false">TEXT(A49,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         <v>0.167361111111111</v>
       </c>
       <c r="E50" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A50,$I$2:$I$16,0))),VLOOKUP(A50,$I$2:$J$16,2,FALSE()),TEXT(A50,"ddd"))</f>
+        <f aca="false">TEXT(A50,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         <v>0.167361111111111</v>
       </c>
       <c r="E51" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A51,$I$2:$I$16,0))),VLOOKUP(A51,$I$2:$J$16,2,FALSE()),TEXT(A51,"ddd"))</f>
+        <f aca="false">TEXT(A51,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
         <v>0.172222222222222</v>
       </c>
       <c r="E52" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A52,$I$2:$I$16,0))),VLOOKUP(A52,$I$2:$J$16,2,FALSE()),TEXT(A52,"ddd"))</f>
+        <f aca="false">TEXT(A52,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         <v>0.173611111111111</v>
       </c>
       <c r="E53" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A53,$I$2:$I$16,0))),VLOOKUP(A53,$I$2:$J$16,2,FALSE()),TEXT(A53,"ddd"))</f>
+        <f aca="false">TEXT(A53,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
         <v>0.176388888888889</v>
       </c>
       <c r="E54" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A54,$I$2:$I$16,0))),VLOOKUP(A54,$I$2:$J$16,2,FALSE()),TEXT(A54,"ddd"))</f>
+        <f aca="false">TEXT(A54,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
         <v>0.174305555555556</v>
       </c>
       <c r="E55" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A55,$I$2:$I$16,0))),VLOOKUP(A55,$I$2:$J$16,2,FALSE()),TEXT(A55,"ddd"))</f>
+        <f aca="false">TEXT(A55,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>0.170833333333333</v>
       </c>
       <c r="E56" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A56,$I$2:$I$16,0))),VLOOKUP(A56,$I$2:$J$16,2,FALSE()),TEXT(A56,"ddd"))</f>
+        <f aca="false">TEXT(A56,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         <v>0.165277777777778</v>
       </c>
       <c r="E57" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A57,$I$2:$I$16,0))),VLOOKUP(A57,$I$2:$J$16,2,FALSE()),TEXT(A57,"ddd"))</f>
+        <f aca="false">TEXT(A57,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
         <v>0.175694444444444</v>
       </c>
       <c r="E58" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A58,$I$2:$I$16,0))),VLOOKUP(A58,$I$2:$J$16,2,FALSE()),TEXT(A58,"ddd"))</f>
+        <f aca="false">TEXT(A58,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
         <v>0.168055555555556</v>
       </c>
       <c r="E59" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A59,$I$2:$I$16,0))),VLOOKUP(A59,$I$2:$J$16,2,FALSE()),TEXT(A59,"ddd"))</f>
+        <f aca="false">TEXT(A59,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
         <v>0.165277777777778</v>
       </c>
       <c r="E60" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A60,$I$2:$I$16,0))),VLOOKUP(A60,$I$2:$J$16,2,FALSE()),TEXT(A60,"ddd"))</f>
+        <f aca="false">TEXT(A60,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         <v>0.16875</v>
       </c>
       <c r="E61" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A61,$I$2:$I$16,0))),VLOOKUP(A61,$I$2:$J$16,2,FALSE()),TEXT(A61,"ddd"))</f>
+        <f aca="false">TEXT(A61,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
         <v>0.166666666666667</v>
       </c>
       <c r="E62" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A62,$I$2:$I$16,0))),VLOOKUP(A62,$I$2:$J$16,2,FALSE()),TEXT(A62,"ddd"))</f>
+        <f aca="false">TEXT(A62,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
         <v>0.166666666666667</v>
       </c>
       <c r="E63" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A63,$I$2:$I$16,0))),VLOOKUP(A63,$I$2:$J$16,2,FALSE()),TEXT(A63,"ddd"))</f>
+        <f aca="false">TEXT(A63,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>0.172916666666667</v>
       </c>
       <c r="E64" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A64,$I$2:$I$16,0))),VLOOKUP(A64,$I$2:$J$16,2,FALSE()),TEXT(A64,"ddd"))</f>
+        <f aca="false">TEXT(A64,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
         <v>0.170833333333333</v>
       </c>
       <c r="E65" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A65,$I$2:$I$16,0))),VLOOKUP(A65,$I$2:$J$16,2,FALSE()),TEXT(A65,"ddd"))</f>
+        <f aca="false">TEXT(A65,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
         <v>0.173611111111111</v>
       </c>
       <c r="E66" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A66,$I$2:$I$16,0))),VLOOKUP(A66,$I$2:$J$16,2,FALSE()),TEXT(A66,"ddd"))</f>
+        <f aca="false">TEXT(A66,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
         <v>0.173611111111111</v>
       </c>
       <c r="E67" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A67,$I$2:$I$16,0))),VLOOKUP(A67,$I$2:$J$16,2,FALSE()),TEXT(A67,"ddd"))</f>
+        <f aca="false">TEXT(A67,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
         <v>0.177083333333333</v>
       </c>
       <c r="E68" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A68,$I$2:$I$16,0))),VLOOKUP(A68,$I$2:$J$16,2,FALSE()),TEXT(A68,"ddd"))</f>
+        <f aca="false">TEXT(A68,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
         <v>0.181944444444444</v>
       </c>
       <c r="E69" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A69,$I$2:$I$16,0))),VLOOKUP(A69,$I$2:$J$16,2,FALSE()),TEXT(A69,"ddd"))</f>
+        <f aca="false">TEXT(A69,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>0.171527777777778</v>
       </c>
       <c r="E70" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A70,$I$2:$I$16,0))),VLOOKUP(A70,$I$2:$J$16,2,FALSE()),TEXT(A70,"ddd"))</f>
+        <f aca="false">TEXT(A70,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
         <v>0.172222222222222</v>
       </c>
       <c r="E71" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A71,$I$2:$I$16,0))),VLOOKUP(A71,$I$2:$J$16,2,FALSE()),TEXT(A71,"ddd"))</f>
+        <f aca="false">TEXT(A71,"ddd")</f>
         <v>Mon</v>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         <v>0.175</v>
       </c>
       <c r="E72" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A72,$I$2:$I$16,0))),VLOOKUP(A72,$I$2:$J$16,2,FALSE()),TEXT(A72,"ddd"))</f>
+        <f aca="false">TEXT(A72,"ddd")</f>
         <v>Tue</v>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         <v>0.175</v>
       </c>
       <c r="E73" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A73,$I$2:$I$16,0))),VLOOKUP(A73,$I$2:$J$16,2,FALSE()),TEXT(A73,"ddd"))</f>
+        <f aca="false">TEXT(A73,"ddd")</f>
         <v>Wed</v>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
         <v>0.172222222222222</v>
       </c>
       <c r="E74" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A74,$I$2:$I$16,0))),VLOOKUP(A74,$I$2:$J$16,2,FALSE()),TEXT(A74,"ddd"))</f>
+        <f aca="false">TEXT(A74,"ddd")</f>
         <v>Thu</v>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
         <v>0.165972222222222</v>
       </c>
       <c r="E75" s="1" t="str">
-        <f aca="false">IF(NOT(ISNA(MATCH(A75,$I$2:$I$16,0))),VLOOKUP(A75,$I$2:$J$16,2,FALSE()),TEXT(A75,"ddd"))</f>
+        <f aca="false">TEXT(A75,"ddd")</f>
         <v>Fri</v>
       </c>
     </row>
